--- a/artfynd/A 60875-2025 artfynd.xlsx
+++ b/artfynd/A 60875-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 60875-2025 artfynd.xlsx
+++ b/artfynd/A 60875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,6 +1144,224 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132499535</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57961</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljungen, Lilla Frö, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>586519</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6269208</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resmo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>George Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>George Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132499563</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ljungen, Lilla Frö, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>586519</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6269208</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resmo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>George Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>George Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60875-2025 artfynd.xlsx
+++ b/artfynd/A 60875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134911342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7253911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100573984</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77939391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499535</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499563</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77939394</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77939400</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77939407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77939397</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1932,6 +1987,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2152161</t>
         </is>
       </c>
     </row>
@@ -2036,8 +2096,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 60875-2025 artfynd.xlsx
+++ b/artfynd/A 60875-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134911342</v>
       </c>
       <c r="B2" t="n">
-        <v>107771</v>
+        <v>107826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
